--- a/admin/Soumissions.xlsx
+++ b/admin/Soumissions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sylvain/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Business/GestionTechnologies/Migration4O/admin/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCFFB73E-CDB0-DD4D-9081-F72986E3D427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B79D0F25-E979-1E4C-9C21-4296E4162C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5560" yWindow="500" windowWidth="28040" windowHeight="17440" xr2:uid="{95DA9C45-7881-A84A-8BA8-7F5BDDABCE18}"/>
+    <workbookView xWindow="-32460" yWindow="900" windowWidth="17820" windowHeight="27360" xr2:uid="{95DA9C45-7881-A84A-8BA8-7F5BDDABCE18}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$I$50</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,12 +39,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="58">
   <si>
     <t>SOUMISSION</t>
-  </si>
-  <si>
-    <t>#2026-03-11-A</t>
   </si>
   <si>
     <t>À L'ATTENTION DE:</t>
@@ -269,6 +266,12 @@
 données extraites, et sera payable 30 jours par chèque au nom de Sylvain Pedneault.</t>
     </r>
   </si>
+  <si>
+    <t>#2026-03-12-A</t>
+  </si>
+  <si>
+    <t>Date BD PL:</t>
+  </si>
 </sst>
 </file>
 
@@ -277,8 +280,8 @@
   <numFmts count="4">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="170" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="172" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -298,13 +301,6 @@
     <font>
       <b/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
@@ -351,6 +347,13 @@
     <font>
       <i/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
@@ -423,53 +426,79 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="172" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="9" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -479,48 +508,14 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="9" fillId="3" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1021,7 +1016,7 @@
     <col min="5" max="5" width="10.83203125" style="3" customWidth="1"/>
     <col min="6" max="6" width="6.6640625" style="3" customWidth="1"/>
     <col min="7" max="7" width="10.83203125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="9.1640625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" style="3" customWidth="1"/>
     <col min="9" max="9" width="13.1640625" style="3" customWidth="1"/>
     <col min="10" max="16384" width="10.83203125" style="3"/>
   </cols>
@@ -1033,7 +1028,7 @@
     </row>
     <row r="2" spans="1:15" ht="22" x14ac:dyDescent="0.3">
       <c r="I2" s="11" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1041,38 +1036,43 @@
     </row>
     <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>3</v>
+      <c r="H4" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="I4" s="39">
+        <v>46077</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C5" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C6" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C7" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="10" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="N7" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
+    </row>
+    <row r="8" spans="1:15" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -1080,36 +1080,36 @@
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H9" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I9" s="5" t="s">
+      <c r="K9" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="O9" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>9</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="L9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="N9" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="O9" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>10</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
@@ -1141,18 +1141,18 @@
       </c>
     </row>
     <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="24"/>
-      <c r="B11" s="35" t="s">
-        <v>34</v>
+      <c r="A11" s="34"/>
+      <c r="B11" s="24" t="s">
+        <v>33</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
       <c r="G11" s="15">
-        <v>65761</v>
+        <v>66129</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ref="H11:H34" si="0">K11</f>
@@ -1160,30 +1160,30 @@
       </c>
       <c r="I11" s="9">
         <f t="shared" ref="I11:I34" si="1">G11*H11</f>
-        <v>3288.05</v>
+        <v>3306.4500000000003</v>
       </c>
       <c r="K11" s="14">
         <v>0.05</v>
       </c>
       <c r="L11" s="9">
         <f t="shared" ref="L11:L34" si="2">$G11*K11</f>
-        <v>3288.05</v>
+        <v>3306.4500000000003</v>
       </c>
       <c r="N11" s="14">
         <v>0.05</v>
       </c>
       <c r="O11" s="9">
         <f t="shared" ref="O11:O34" si="3">$G11*N11</f>
-        <v>3288.05</v>
+        <v>3306.4500000000003</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="25"/>
-      <c r="B12" s="35" t="s">
-        <v>34</v>
+      <c r="A12" s="35"/>
+      <c r="B12" s="24" t="s">
+        <v>33</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
@@ -1215,20 +1215,20 @@
       </c>
     </row>
     <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" s="42" t="s">
-        <v>34</v>
+      <c r="A13" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="31" t="s">
+        <v>33</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D13" s="16"/>
       <c r="E13" s="16"/>
       <c r="F13" s="16"/>
       <c r="G13" s="17">
-        <v>6609</v>
+        <v>6266</v>
       </c>
       <c r="H13" s="18">
         <f t="shared" si="0"/>
@@ -1236,36 +1236,36 @@
       </c>
       <c r="I13" s="19">
         <f t="shared" si="1"/>
-        <v>6609</v>
+        <v>6266</v>
       </c>
       <c r="K13" s="18">
         <v>1</v>
       </c>
       <c r="L13" s="9">
         <f t="shared" si="2"/>
-        <v>6609</v>
+        <v>6266</v>
       </c>
       <c r="N13" s="18">
         <v>0.5</v>
       </c>
       <c r="O13" s="9">
         <f t="shared" si="3"/>
-        <v>3304.5</v>
+        <v>3133</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="27"/>
-      <c r="B14" s="35" t="s">
-        <v>34</v>
+      <c r="A14" s="34"/>
+      <c r="B14" s="24" t="s">
+        <v>33</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
       <c r="G14" s="15">
-        <v>14082</v>
+        <v>14179</v>
       </c>
       <c r="H14" s="14">
         <f t="shared" si="0"/>
@@ -1273,36 +1273,36 @@
       </c>
       <c r="I14" s="9">
         <f t="shared" si="1"/>
-        <v>704.1</v>
+        <v>708.95</v>
       </c>
       <c r="K14" s="14">
         <v>0.05</v>
       </c>
       <c r="L14" s="9">
         <f t="shared" si="2"/>
-        <v>704.1</v>
+        <v>708.95</v>
       </c>
       <c r="N14" s="14">
         <v>0.05</v>
       </c>
       <c r="O14" s="9">
         <f t="shared" si="3"/>
-        <v>704.1</v>
+        <v>708.95</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="27"/>
-      <c r="B15" s="35" t="s">
-        <v>34</v>
+      <c r="A15" s="34"/>
+      <c r="B15" s="24" t="s">
+        <v>33</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
       <c r="G15" s="15">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H15" s="14">
         <f t="shared" si="0"/>
@@ -1310,30 +1310,30 @@
       </c>
       <c r="I15" s="9">
         <f t="shared" si="1"/>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K15" s="14">
         <v>1</v>
       </c>
       <c r="L15" s="9">
         <f t="shared" si="2"/>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N15" s="14">
         <v>1</v>
       </c>
       <c r="O15" s="9">
         <f t="shared" si="3"/>
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="27"/>
-      <c r="B16" s="35" t="s">
-        <v>34</v>
+      <c r="A16" s="34"/>
+      <c r="B16" s="24" t="s">
+        <v>33</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
@@ -1365,12 +1365,12 @@
       </c>
     </row>
     <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="25"/>
-      <c r="B17" s="35" t="s">
-        <v>34</v>
+      <c r="A17" s="35"/>
+      <c r="B17" s="24" t="s">
+        <v>33</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
@@ -1402,14 +1402,14 @@
       </c>
     </row>
     <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="B18" s="42" t="s">
-        <v>34</v>
+      <c r="A18" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="31" t="s">
+        <v>33</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
@@ -1441,12 +1441,12 @@
       </c>
     </row>
     <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="27"/>
-      <c r="B19" s="35" t="s">
-        <v>34</v>
+      <c r="A19" s="34"/>
+      <c r="B19" s="24" t="s">
+        <v>33</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
@@ -1478,18 +1478,18 @@
       </c>
     </row>
     <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="27"/>
-      <c r="B20" s="35" t="s">
-        <v>34</v>
+      <c r="A20" s="34"/>
+      <c r="B20" s="24" t="s">
+        <v>33</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
       <c r="G20" s="15">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="H20" s="14">
         <f t="shared" si="0"/>
@@ -1497,36 +1497,36 @@
       </c>
       <c r="I20" s="9">
         <f t="shared" si="1"/>
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="K20" s="14">
         <v>1</v>
       </c>
       <c r="L20" s="9">
         <f t="shared" si="2"/>
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N20" s="14">
         <v>1</v>
       </c>
       <c r="O20" s="9">
         <f t="shared" si="3"/>
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="27"/>
-      <c r="B21" s="35" t="s">
-        <v>34</v>
+      <c r="A21" s="34"/>
+      <c r="B21" s="24" t="s">
+        <v>33</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
       <c r="G21" s="15">
-        <v>2364</v>
+        <v>2556</v>
       </c>
       <c r="H21" s="14">
         <f t="shared" si="0"/>
@@ -1534,30 +1534,30 @@
       </c>
       <c r="I21" s="9">
         <f t="shared" si="1"/>
-        <v>2364</v>
+        <v>2556</v>
       </c>
       <c r="K21" s="14">
         <v>1</v>
       </c>
       <c r="L21" s="9">
         <f t="shared" si="2"/>
-        <v>2364</v>
+        <v>2556</v>
       </c>
       <c r="N21" s="14">
         <v>0.5</v>
       </c>
       <c r="O21" s="9">
         <f t="shared" si="3"/>
-        <v>1182</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="27"/>
-      <c r="B22" s="35" t="s">
-        <v>34</v>
+      <c r="A22" s="34"/>
+      <c r="B22" s="24" t="s">
+        <v>33</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
@@ -1589,12 +1589,12 @@
       </c>
     </row>
     <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="25"/>
-      <c r="B23" s="35" t="s">
-        <v>34</v>
+      <c r="A23" s="35"/>
+      <c r="B23" s="24" t="s">
+        <v>33</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
@@ -1626,14 +1626,14 @@
       </c>
     </row>
     <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24" s="42" t="s">
-        <v>34</v>
+      <c r="A24" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="31" t="s">
+        <v>33</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D24" s="16"/>
       <c r="E24" s="16"/>
@@ -1665,12 +1665,12 @@
       </c>
     </row>
     <row r="25" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="27"/>
-      <c r="B25" s="35" t="s">
-        <v>34</v>
+      <c r="A25" s="34"/>
+      <c r="B25" s="24" t="s">
+        <v>33</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
@@ -1702,12 +1702,12 @@
       </c>
     </row>
     <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="27"/>
-      <c r="B26" s="35" t="s">
-        <v>34</v>
+      <c r="A26" s="34"/>
+      <c r="B26" s="24" t="s">
+        <v>33</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
@@ -1739,12 +1739,12 @@
       </c>
     </row>
     <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="27"/>
-      <c r="B27" s="35" t="s">
-        <v>34</v>
+      <c r="A27" s="34"/>
+      <c r="B27" s="24" t="s">
+        <v>33</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
@@ -1776,12 +1776,12 @@
       </c>
     </row>
     <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="27"/>
-      <c r="B28" s="35" t="s">
-        <v>34</v>
+      <c r="A28" s="34"/>
+      <c r="B28" s="24" t="s">
+        <v>33</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
@@ -1813,12 +1813,12 @@
       </c>
     </row>
     <row r="29" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="25"/>
-      <c r="B29" s="35" t="s">
-        <v>34</v>
+      <c r="A29" s="35"/>
+      <c r="B29" s="24" t="s">
+        <v>33</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
@@ -1850,20 +1850,20 @@
       </c>
     </row>
     <row r="30" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="B30" s="42" t="s">
-        <v>34</v>
+      <c r="A30" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="B30" s="31" t="s">
+        <v>33</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D30" s="16"/>
       <c r="E30" s="16"/>
       <c r="F30" s="16"/>
       <c r="G30" s="17">
-        <v>14602</v>
+        <v>14590</v>
       </c>
       <c r="H30" s="18">
         <f t="shared" si="0"/>
@@ -1871,30 +1871,30 @@
       </c>
       <c r="I30" s="19">
         <f t="shared" si="1"/>
-        <v>14602</v>
+        <v>14590</v>
       </c>
       <c r="K30" s="18">
         <v>1</v>
       </c>
       <c r="L30" s="9">
         <f t="shared" si="2"/>
-        <v>14602</v>
+        <v>14590</v>
       </c>
       <c r="N30" s="18">
         <v>0.5</v>
       </c>
       <c r="O30" s="9">
         <f t="shared" si="3"/>
-        <v>7301</v>
+        <v>7295</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="28"/>
-      <c r="B31" s="35" t="s">
+      <c r="A31" s="37"/>
+      <c r="B31" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" s="8" t="s">
         <v>34</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>35</v>
       </c>
       <c r="D31" s="8"/>
       <c r="E31" s="8"/>
@@ -1926,18 +1926,18 @@
       </c>
     </row>
     <row r="32" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="28"/>
-      <c r="B32" s="35" t="s">
-        <v>34</v>
+      <c r="A32" s="37"/>
+      <c r="B32" s="24" t="s">
+        <v>33</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D32" s="8"/>
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
       <c r="G32" s="15">
-        <v>5536</v>
+        <v>5619</v>
       </c>
       <c r="H32" s="14">
         <f t="shared" si="0"/>
@@ -1945,30 +1945,30 @@
       </c>
       <c r="I32" s="9">
         <f t="shared" si="1"/>
-        <v>5536</v>
+        <v>5619</v>
       </c>
       <c r="K32" s="14">
         <v>1</v>
       </c>
       <c r="L32" s="9">
         <f t="shared" si="2"/>
-        <v>5536</v>
+        <v>5619</v>
       </c>
       <c r="N32" s="14">
         <v>1</v>
       </c>
       <c r="O32" s="9">
         <f t="shared" si="3"/>
-        <v>5536</v>
+        <v>5619</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="28"/>
-      <c r="B33" s="35" t="s">
-        <v>34</v>
+      <c r="A33" s="37"/>
+      <c r="B33" s="24" t="s">
+        <v>33</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
@@ -2000,18 +2000,18 @@
       </c>
     </row>
     <row r="34" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="28"/>
-      <c r="B34" s="35" t="s">
-        <v>34</v>
+      <c r="A34" s="37"/>
+      <c r="B34" s="24" t="s">
+        <v>33</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
       <c r="F34" s="8"/>
       <c r="G34" s="15">
-        <v>1057</v>
+        <v>1070</v>
       </c>
       <c r="H34" s="14">
         <f t="shared" si="0"/>
@@ -2019,30 +2019,30 @@
       </c>
       <c r="I34" s="9">
         <f t="shared" si="1"/>
-        <v>264.25</v>
+        <v>267.5</v>
       </c>
       <c r="K34" s="14">
         <v>0.25</v>
       </c>
       <c r="L34" s="9">
         <f t="shared" si="2"/>
-        <v>264.25</v>
+        <v>267.5</v>
       </c>
       <c r="N34" s="14">
         <v>0.25</v>
       </c>
       <c r="O34" s="9">
         <f t="shared" si="3"/>
-        <v>264.25</v>
+        <v>267.5</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C36" s="16"/>
       <c r="D36" s="16"/>
@@ -2050,33 +2050,33 @@
       <c r="F36" s="16"/>
       <c r="G36" s="16"/>
       <c r="H36" s="16"/>
-      <c r="I36" s="29" t="s">
+      <c r="I36" s="23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="25" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="B38" s="8" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="B37" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="C37" s="31"/>
-      <c r="D37" s="31"/>
-      <c r="E37" s="31"/>
-      <c r="F37" s="31"/>
-      <c r="G37" s="31"/>
-      <c r="H37" s="31"/>
-      <c r="I37" s="32" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>39</v>
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
@@ -2084,16 +2084,16 @@
       <c r="F38" s="8"/>
       <c r="G38" s="8"/>
       <c r="H38" s="8"/>
-      <c r="I38" s="33" t="s">
-        <v>38</v>
+      <c r="I38" s="25" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="30" t="s">
-        <v>53</v>
+      <c r="A39" s="24" t="s">
+        <v>52</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
@@ -2101,12 +2101,12 @@
       <c r="F39" s="8"/>
       <c r="G39" s="8"/>
       <c r="H39" s="8"/>
-      <c r="I39" s="33" t="s">
-        <v>38</v>
+      <c r="I39" s="25" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="40" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="23"/>
+      <c r="A40" s="7"/>
       <c r="B40" s="8"/>
       <c r="I40" s="1"/>
     </row>
@@ -2118,28 +2118,28 @@
       <c r="E41" s="20"/>
       <c r="F41" s="20"/>
       <c r="G41" s="20"/>
-      <c r="H41" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="I41" s="39">
-        <f>SUM(I4:I39)</f>
-        <v>36203.4</v>
+      <c r="H41" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="I41" s="29">
+        <f>SUM(I10:I39)</f>
+        <v>36152.9</v>
       </c>
     </row>
     <row r="42" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="43" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="35" t="s">
-        <v>37</v>
+      <c r="A43" s="24" t="s">
+        <v>36</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
       <c r="E43" s="8"/>
       <c r="F43" s="8"/>
       <c r="G43" s="8">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="H43" s="9">
         <f>-N13</f>
@@ -2147,26 +2147,26 @@
       </c>
       <c r="I43" s="22">
         <f t="shared" ref="I43" si="4">G43*H43</f>
-        <v>-127.5</v>
+        <v>-136</v>
       </c>
       <c r="K43" s="13"/>
     </row>
     <row r="44" spans="1:15" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="37" t="s">
-        <v>54</v>
-      </c>
-      <c r="C44" s="37"/>
-      <c r="D44" s="37"/>
-      <c r="E44" s="37"/>
-      <c r="F44" s="37"/>
+      <c r="A44" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B44" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="C44" s="38"/>
+      <c r="D44" s="38"/>
+      <c r="E44" s="38"/>
+      <c r="F44" s="38"/>
       <c r="G44" s="8"/>
       <c r="H44" s="14"/>
-      <c r="I44" s="41">
+      <c r="I44" s="30">
         <f>-O49</f>
-        <v>-12442</v>
+        <v>-12360.5</v>
       </c>
       <c r="K44" s="13"/>
     </row>
@@ -2180,65 +2180,65 @@
       <c r="A46" s="7"/>
     </row>
     <row r="47" spans="1:15" ht="26" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="40"/>
-      <c r="B47" s="40"/>
-      <c r="C47" s="40"/>
-      <c r="D47" s="40"/>
-      <c r="E47" s="40"/>
-      <c r="F47" s="40"/>
-      <c r="G47" s="40"/>
-      <c r="H47" s="44" t="s">
-        <v>47</v>
-      </c>
-      <c r="I47" s="43">
+      <c r="A47" s="26"/>
+      <c r="B47" s="26"/>
+      <c r="C47" s="26"/>
+      <c r="D47" s="26"/>
+      <c r="E47" s="26"/>
+      <c r="F47" s="26"/>
+      <c r="G47" s="26"/>
+      <c r="H47" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="I47" s="40">
         <f>I41+SUM(I43:I45)</f>
-        <v>23633.9</v>
+        <v>23656.400000000001</v>
       </c>
       <c r="L47" s="21">
         <f>SUM(L10:L46)</f>
-        <v>36203.4</v>
+        <v>36152.9</v>
       </c>
       <c r="O47" s="21">
         <f>SUM(O10:O46)</f>
-        <v>23761.4</v>
+        <v>23792.400000000001</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A48" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="B48" s="34"/>
-      <c r="C48" s="34"/>
-      <c r="D48" s="34"/>
-      <c r="E48" s="34"/>
-      <c r="F48" s="34"/>
-      <c r="G48" s="34"/>
+      <c r="A48" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="33"/>
+      <c r="C48" s="33"/>
+      <c r="D48" s="33"/>
+      <c r="E48" s="33"/>
+      <c r="F48" s="33"/>
+      <c r="G48" s="33"/>
       <c r="I48" s="10" t="str">
         <f>"+taxes"</f>
         <v>+taxes</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A49" s="34"/>
-      <c r="B49" s="34"/>
-      <c r="C49" s="34"/>
-      <c r="D49" s="34"/>
-      <c r="E49" s="34"/>
-      <c r="F49" s="34"/>
-      <c r="G49" s="34"/>
+      <c r="A49" s="33"/>
+      <c r="B49" s="33"/>
+      <c r="C49" s="33"/>
+      <c r="D49" s="33"/>
+      <c r="E49" s="33"/>
+      <c r="F49" s="33"/>
+      <c r="G49" s="33"/>
       <c r="O49" s="12">
         <f>L47-O47</f>
-        <v>12442</v>
+        <v>12360.5</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A50" s="34"/>
-      <c r="B50" s="34"/>
-      <c r="C50" s="34"/>
-      <c r="D50" s="34"/>
-      <c r="E50" s="34"/>
-      <c r="F50" s="34"/>
-      <c r="G50" s="34"/>
+      <c r="A50" s="33"/>
+      <c r="B50" s="33"/>
+      <c r="C50" s="33"/>
+      <c r="D50" s="33"/>
+      <c r="E50" s="33"/>
+      <c r="F50" s="33"/>
+      <c r="G50" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -2278,45 +2278,45 @@
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K10:K34">
-    <cfRule type="cellIs" dxfId="11" priority="9" operator="equal">
+  <conditionalFormatting sqref="I45">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
       <formula>0.25</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K10:K34">
+    <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
+      <formula>0.05</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="10" operator="equal">
+      <formula>0.25</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="11" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="12" operator="equal">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N10:N34">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="6" operator="equal">
       <formula>0.25</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
-      <formula>0.5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I45">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
-      <formula>0.05</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
-      <formula>0.25</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="8" operator="equal">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>

--- a/admin/Soumissions.xlsx
+++ b/admin/Soumissions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Business/GestionTechnologies/Migration4O/admin/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B79D0F25-E979-1E4C-9C21-4296E4162C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2183DC64-95A7-3A42-8492-82BFDADE20AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32460" yWindow="900" windowWidth="17820" windowHeight="27360" xr2:uid="{95DA9C45-7881-A84A-8BA8-7F5BDDABCE18}"/>
+    <workbookView xWindow="8140" yWindow="1040" windowWidth="34440" windowHeight="30180" xr2:uid="{95DA9C45-7881-A84A-8BA8-7F5BDDABCE18}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="60">
   <si>
     <t>SOUMISSION</t>
   </si>
@@ -271,6 +271,12 @@
   </si>
   <si>
     <t>Date BD PL:</t>
+  </si>
+  <si>
+    <t>Ré-exports:</t>
+  </si>
+  <si>
+    <t>Deux exports complets additionnels, au maximum 18 mois après le premier export</t>
   </si>
 </sst>
 </file>
@@ -359,7 +365,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -381,6 +387,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,9 +440,6 @@
   </cellStyleXfs>
   <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -496,6 +505,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -514,8 +525,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1011,1234 +1021,1240 @@
   <dimension ref="A1:O50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" style="3" customWidth="1"/>
-    <col min="2" max="4" width="10.83203125" style="3"/>
-    <col min="5" max="5" width="10.83203125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="6.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="13.1640625" style="3" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="3"/>
+    <col min="1" max="1" width="12.33203125" style="2" customWidth="1"/>
+    <col min="2" max="4" width="10.83203125" style="2"/>
+    <col min="5" max="5" width="10.83203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="6.6640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="13.1640625" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="29" x14ac:dyDescent="0.35">
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="22" x14ac:dyDescent="0.3">
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="10" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I3" s="7"/>
+      <c r="I3" s="6"/>
     </row>
     <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="A4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="I4" s="39">
+      <c r="I4" s="32">
         <v>46077</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="K7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="N7" s="3" t="s">
+      <c r="N7" s="2" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="5" t="s">
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="K9" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="L9" s="5" t="s">
+      <c r="L9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="N9" s="6" t="s">
+      <c r="N9" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="O9" s="5" t="s">
+      <c r="O9" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="34" t="s">
+      <c r="A10" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="8" t="s">
+      <c r="B10" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="15">
-        <v>1</v>
-      </c>
-      <c r="H10" s="14">
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="14">
+        <v>1</v>
+      </c>
+      <c r="H10" s="13">
         <f>K10</f>
         <v>1</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="8">
         <f>G10*H10</f>
         <v>1</v>
       </c>
-      <c r="K10" s="14">
-        <v>1</v>
-      </c>
-      <c r="L10" s="9">
+      <c r="K10" s="13">
+        <v>1</v>
+      </c>
+      <c r="L10" s="8">
         <f>$G10*K10</f>
         <v>1</v>
       </c>
-      <c r="N10" s="14">
-        <v>1</v>
-      </c>
-      <c r="O10" s="9">
+      <c r="N10" s="13">
+        <v>1</v>
+      </c>
+      <c r="O10" s="8">
         <f>$G10*N10</f>
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="34"/>
-      <c r="B11" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="8" t="s">
+      <c r="A11" s="35"/>
+      <c r="B11" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="15">
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="14">
         <v>66129</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H11" s="13">
         <f t="shared" ref="H11:H34" si="0">K11</f>
         <v>0.05</v>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="8">
         <f t="shared" ref="I11:I34" si="1">G11*H11</f>
         <v>3306.4500000000003</v>
       </c>
-      <c r="K11" s="14">
+      <c r="K11" s="13">
         <v>0.05</v>
       </c>
-      <c r="L11" s="9">
+      <c r="L11" s="8">
         <f t="shared" ref="L11:L34" si="2">$G11*K11</f>
         <v>3306.4500000000003</v>
       </c>
-      <c r="N11" s="14">
+      <c r="N11" s="13">
         <v>0.05</v>
       </c>
-      <c r="O11" s="9">
+      <c r="O11" s="8">
         <f t="shared" ref="O11:O34" si="3">$G11*N11</f>
         <v>3306.4500000000003</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="35"/>
-      <c r="B12" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="8" t="s">
+      <c r="A12" s="36"/>
+      <c r="B12" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="15">
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="14">
         <v>2</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H12" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="8">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="K12" s="14">
-        <v>1</v>
-      </c>
-      <c r="L12" s="9">
+      <c r="K12" s="13">
+        <v>1</v>
+      </c>
+      <c r="L12" s="8">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N12" s="14">
-        <v>1</v>
-      </c>
-      <c r="O12" s="9">
+      <c r="N12" s="13">
+        <v>1</v>
+      </c>
+      <c r="O12" s="8">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="36" t="s">
+      <c r="A13" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="16" t="s">
+      <c r="B13" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="17">
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="16">
         <v>6266</v>
       </c>
-      <c r="H13" s="18">
+      <c r="H13" s="17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I13" s="19">
+      <c r="I13" s="18">
         <f t="shared" si="1"/>
         <v>6266</v>
       </c>
-      <c r="K13" s="18">
-        <v>1</v>
-      </c>
-      <c r="L13" s="9">
+      <c r="K13" s="17">
+        <v>1</v>
+      </c>
+      <c r="L13" s="8">
         <f t="shared" si="2"/>
         <v>6266</v>
       </c>
-      <c r="N13" s="18">
+      <c r="N13" s="17">
         <v>0.5</v>
       </c>
-      <c r="O13" s="9">
+      <c r="O13" s="8">
         <f t="shared" si="3"/>
         <v>3133</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="34"/>
-      <c r="B14" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="8" t="s">
+      <c r="A14" s="35"/>
+      <c r="B14" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="15">
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="14">
         <v>14179</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H14" s="13">
         <f t="shared" si="0"/>
         <v>0.05</v>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="8">
         <f t="shared" si="1"/>
         <v>708.95</v>
       </c>
-      <c r="K14" s="14">
+      <c r="K14" s="13">
         <v>0.05</v>
       </c>
-      <c r="L14" s="9">
+      <c r="L14" s="8">
         <f t="shared" si="2"/>
         <v>708.95</v>
       </c>
-      <c r="N14" s="14">
+      <c r="N14" s="13">
         <v>0.05</v>
       </c>
-      <c r="O14" s="9">
+      <c r="O14" s="8">
         <f t="shared" si="3"/>
         <v>708.95</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="34"/>
-      <c r="B15" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="8" t="s">
+      <c r="A15" s="35"/>
+      <c r="B15" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="15">
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="14">
         <v>46</v>
       </c>
-      <c r="H15" s="14">
+      <c r="H15" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="8">
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
-      <c r="K15" s="14">
-        <v>1</v>
-      </c>
-      <c r="L15" s="9">
+      <c r="K15" s="13">
+        <v>1</v>
+      </c>
+      <c r="L15" s="8">
         <f t="shared" si="2"/>
         <v>46</v>
       </c>
-      <c r="N15" s="14">
-        <v>1</v>
-      </c>
-      <c r="O15" s="9">
+      <c r="N15" s="13">
+        <v>1</v>
+      </c>
+      <c r="O15" s="8">
         <f t="shared" si="3"/>
         <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="34"/>
-      <c r="B16" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="8" t="s">
+      <c r="A16" s="35"/>
+      <c r="B16" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="15">
-        <v>1</v>
-      </c>
-      <c r="H16" s="14">
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="14">
+        <v>1</v>
+      </c>
+      <c r="H16" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I16" s="9">
+      <c r="I16" s="8">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K16" s="14">
-        <v>1</v>
-      </c>
-      <c r="L16" s="9">
+      <c r="K16" s="13">
+        <v>1</v>
+      </c>
+      <c r="L16" s="8">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="N16" s="14">
-        <v>1</v>
-      </c>
-      <c r="O16" s="9">
+      <c r="N16" s="13">
+        <v>1</v>
+      </c>
+      <c r="O16" s="8">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="35"/>
-      <c r="B17" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="8" t="s">
+      <c r="A17" s="36"/>
+      <c r="B17" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="15">
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="14">
         <v>0</v>
       </c>
-      <c r="H17" s="14">
+      <c r="H17" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I17" s="9">
+      <c r="I17" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K17" s="14">
-        <v>1</v>
-      </c>
-      <c r="L17" s="9">
+      <c r="K17" s="13">
+        <v>1</v>
+      </c>
+      <c r="L17" s="8">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N17" s="14">
-        <v>1</v>
-      </c>
-      <c r="O17" s="9">
+      <c r="N17" s="13">
+        <v>1</v>
+      </c>
+      <c r="O17" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="36" t="s">
+      <c r="A18" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="16" t="s">
+      <c r="B18" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="17">
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="16">
         <v>4</v>
       </c>
-      <c r="H18" s="18">
+      <c r="H18" s="17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I18" s="19">
+      <c r="I18" s="18">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="K18" s="18">
-        <v>1</v>
-      </c>
-      <c r="L18" s="9">
+      <c r="K18" s="17">
+        <v>1</v>
+      </c>
+      <c r="L18" s="8">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="N18" s="18">
-        <v>1</v>
-      </c>
-      <c r="O18" s="9">
+      <c r="N18" s="17">
+        <v>1</v>
+      </c>
+      <c r="O18" s="8">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="34"/>
-      <c r="B19" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" s="8" t="s">
+      <c r="A19" s="35"/>
+      <c r="B19" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="15">
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="14">
         <v>28</v>
       </c>
-      <c r="H19" s="14">
+      <c r="H19" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I19" s="9">
+      <c r="I19" s="8">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
-      <c r="K19" s="14">
-        <v>1</v>
-      </c>
-      <c r="L19" s="9">
+      <c r="K19" s="13">
+        <v>1</v>
+      </c>
+      <c r="L19" s="8">
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="N19" s="14">
-        <v>1</v>
-      </c>
-      <c r="O19" s="9">
+      <c r="N19" s="13">
+        <v>1</v>
+      </c>
+      <c r="O19" s="8">
         <f t="shared" si="3"/>
         <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="34"/>
-      <c r="B20" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" s="8" t="s">
+      <c r="A20" s="35"/>
+      <c r="B20" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="15">
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="14">
         <v>523</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I20" s="9">
+      <c r="I20" s="8">
         <f t="shared" si="1"/>
         <v>523</v>
       </c>
-      <c r="K20" s="14">
-        <v>1</v>
-      </c>
-      <c r="L20" s="9">
+      <c r="K20" s="13">
+        <v>1</v>
+      </c>
+      <c r="L20" s="8">
         <f t="shared" si="2"/>
         <v>523</v>
       </c>
-      <c r="N20" s="14">
-        <v>1</v>
-      </c>
-      <c r="O20" s="9">
+      <c r="N20" s="13">
+        <v>1</v>
+      </c>
+      <c r="O20" s="8">
         <f t="shared" si="3"/>
         <v>523</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="34"/>
-      <c r="B21" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C21" s="8" t="s">
+      <c r="A21" s="35"/>
+      <c r="B21" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="15">
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="14">
         <v>2556</v>
       </c>
-      <c r="H21" s="14">
+      <c r="H21" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I21" s="9">
+      <c r="I21" s="8">
         <f t="shared" si="1"/>
         <v>2556</v>
       </c>
-      <c r="K21" s="14">
-        <v>1</v>
-      </c>
-      <c r="L21" s="9">
+      <c r="K21" s="13">
+        <v>1</v>
+      </c>
+      <c r="L21" s="8">
         <f t="shared" si="2"/>
         <v>2556</v>
       </c>
-      <c r="N21" s="14">
+      <c r="N21" s="13">
         <v>0.5</v>
       </c>
-      <c r="O21" s="9">
+      <c r="O21" s="8">
         <f t="shared" si="3"/>
         <v>1278</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="34"/>
-      <c r="B22" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="8" t="s">
+      <c r="A22" s="35"/>
+      <c r="B22" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="15">
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="14">
         <v>523</v>
       </c>
-      <c r="H22" s="14">
+      <c r="H22" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I22" s="9">
+      <c r="I22" s="8">
         <f t="shared" si="1"/>
         <v>523</v>
       </c>
-      <c r="K22" s="14">
-        <v>1</v>
-      </c>
-      <c r="L22" s="9">
+      <c r="K22" s="13">
+        <v>1</v>
+      </c>
+      <c r="L22" s="8">
         <f t="shared" si="2"/>
         <v>523</v>
       </c>
-      <c r="N22" s="14">
-        <v>1</v>
-      </c>
-      <c r="O22" s="9">
+      <c r="N22" s="13">
+        <v>1</v>
+      </c>
+      <c r="O22" s="8">
         <f t="shared" si="3"/>
         <v>523</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="35"/>
-      <c r="B23" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23" s="8" t="s">
+      <c r="A23" s="36"/>
+      <c r="B23" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="15">
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="14">
         <v>1309</v>
       </c>
-      <c r="H23" s="14">
+      <c r="H23" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I23" s="9">
+      <c r="I23" s="8">
         <f t="shared" si="1"/>
         <v>1309</v>
       </c>
-      <c r="K23" s="14">
-        <v>1</v>
-      </c>
-      <c r="L23" s="9">
+      <c r="K23" s="13">
+        <v>1</v>
+      </c>
+      <c r="L23" s="8">
         <f t="shared" si="2"/>
         <v>1309</v>
       </c>
-      <c r="N23" s="14">
+      <c r="N23" s="13">
         <v>0.5</v>
       </c>
-      <c r="O23" s="9">
+      <c r="O23" s="8">
         <f t="shared" si="3"/>
         <v>654.5</v>
       </c>
     </row>
     <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="36" t="s">
+      <c r="A24" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" s="16" t="s">
+      <c r="B24" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="17">
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="16">
         <v>121</v>
       </c>
-      <c r="H24" s="18">
+      <c r="H24" s="17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I24" s="19">
+      <c r="I24" s="18">
         <f t="shared" si="1"/>
         <v>121</v>
       </c>
-      <c r="K24" s="18">
-        <v>1</v>
-      </c>
-      <c r="L24" s="9">
+      <c r="K24" s="17">
+        <v>1</v>
+      </c>
+      <c r="L24" s="8">
         <f t="shared" si="2"/>
         <v>121</v>
       </c>
-      <c r="N24" s="18">
-        <v>1</v>
-      </c>
-      <c r="O24" s="9">
+      <c r="N24" s="17">
+        <v>1</v>
+      </c>
+      <c r="O24" s="8">
         <f t="shared" si="3"/>
         <v>121</v>
       </c>
     </row>
     <row r="25" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="34"/>
-      <c r="B25" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" s="8" t="s">
+      <c r="A25" s="35"/>
+      <c r="B25" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="15">
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="14">
         <v>7</v>
       </c>
-      <c r="H25" s="14">
+      <c r="H25" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I25" s="9">
+      <c r="I25" s="8">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="K25" s="14">
-        <v>1</v>
-      </c>
-      <c r="L25" s="9">
+      <c r="K25" s="13">
+        <v>1</v>
+      </c>
+      <c r="L25" s="8">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="N25" s="14">
-        <v>1</v>
-      </c>
-      <c r="O25" s="9">
+      <c r="N25" s="13">
+        <v>1</v>
+      </c>
+      <c r="O25" s="8">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="34"/>
-      <c r="B26" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C26" s="8" t="s">
+      <c r="A26" s="35"/>
+      <c r="B26" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="15">
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="14">
         <v>3</v>
       </c>
-      <c r="H26" s="14">
+      <c r="H26" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I26" s="9">
+      <c r="I26" s="8">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K26" s="14">
-        <v>1</v>
-      </c>
-      <c r="L26" s="9">
+      <c r="K26" s="13">
+        <v>1</v>
+      </c>
+      <c r="L26" s="8">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="N26" s="14">
-        <v>1</v>
-      </c>
-      <c r="O26" s="9">
+      <c r="N26" s="13">
+        <v>1</v>
+      </c>
+      <c r="O26" s="8">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="34"/>
-      <c r="B27" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C27" s="8" t="s">
+      <c r="A27" s="35"/>
+      <c r="B27" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="15">
-        <v>1</v>
-      </c>
-      <c r="H27" s="14">
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="14">
+        <v>1</v>
+      </c>
+      <c r="H27" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I27" s="9">
+      <c r="I27" s="8">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K27" s="14">
-        <v>1</v>
-      </c>
-      <c r="L27" s="9">
+      <c r="K27" s="13">
+        <v>1</v>
+      </c>
+      <c r="L27" s="8">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="N27" s="14">
-        <v>1</v>
-      </c>
-      <c r="O27" s="9">
+      <c r="N27" s="13">
+        <v>1</v>
+      </c>
+      <c r="O27" s="8">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="34"/>
-      <c r="B28" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C28" s="8" t="s">
+      <c r="A28" s="35"/>
+      <c r="B28" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="15">
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="14">
         <v>0</v>
       </c>
-      <c r="H28" s="14">
+      <c r="H28" s="13">
         <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
-      <c r="I28" s="9">
+      <c r="I28" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K28" s="14">
+      <c r="K28" s="13">
         <v>0.25</v>
       </c>
-      <c r="L28" s="9">
+      <c r="L28" s="8">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N28" s="14">
+      <c r="N28" s="13">
         <v>0.25</v>
       </c>
-      <c r="O28" s="9">
+      <c r="O28" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="35"/>
-      <c r="B29" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C29" s="8" t="s">
+      <c r="A29" s="36"/>
+      <c r="B29" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="15">
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="14">
         <v>0</v>
       </c>
-      <c r="H29" s="14">
+      <c r="H29" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I29" s="9">
+      <c r="I29" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K29" s="14">
-        <v>1</v>
-      </c>
-      <c r="L29" s="9">
+      <c r="K29" s="13">
+        <v>1</v>
+      </c>
+      <c r="L29" s="8">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N29" s="14">
-        <v>1</v>
-      </c>
-      <c r="O29" s="9">
+      <c r="N29" s="13">
+        <v>1</v>
+      </c>
+      <c r="O29" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="36" t="s">
+      <c r="A30" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="B30" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="C30" s="16" t="s">
+      <c r="B30" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="17">
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="16">
         <v>14590</v>
       </c>
-      <c r="H30" s="18">
+      <c r="H30" s="17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I30" s="19">
+      <c r="I30" s="18">
         <f t="shared" si="1"/>
         <v>14590</v>
       </c>
-      <c r="K30" s="18">
-        <v>1</v>
-      </c>
-      <c r="L30" s="9">
+      <c r="K30" s="17">
+        <v>1</v>
+      </c>
+      <c r="L30" s="8">
         <f t="shared" si="2"/>
         <v>14590</v>
       </c>
-      <c r="N30" s="18">
+      <c r="N30" s="17">
         <v>0.5</v>
       </c>
-      <c r="O30" s="9">
+      <c r="O30" s="8">
         <f t="shared" si="3"/>
         <v>7295</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="37"/>
-      <c r="B31" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C31" s="8" t="s">
+      <c r="A31" s="38"/>
+      <c r="B31" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="15">
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="14">
         <v>1048</v>
       </c>
-      <c r="H31" s="14">
+      <c r="H31" s="13">
         <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
-      <c r="I31" s="9">
+      <c r="I31" s="8">
         <f t="shared" si="1"/>
         <v>262</v>
       </c>
-      <c r="K31" s="14">
+      <c r="K31" s="13">
         <v>0.25</v>
       </c>
-      <c r="L31" s="9">
+      <c r="L31" s="8">
         <f t="shared" si="2"/>
         <v>262</v>
       </c>
-      <c r="N31" s="14">
+      <c r="N31" s="13">
         <v>0.25</v>
       </c>
-      <c r="O31" s="9">
+      <c r="O31" s="8">
         <f t="shared" si="3"/>
         <v>262</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="37"/>
-      <c r="B32" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" s="8" t="s">
+      <c r="A32" s="38"/>
+      <c r="B32" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="15">
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="14">
         <v>5619</v>
       </c>
-      <c r="H32" s="14">
+      <c r="H32" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I32" s="9">
+      <c r="I32" s="8">
         <f t="shared" si="1"/>
         <v>5619</v>
       </c>
-      <c r="K32" s="14">
-        <v>1</v>
-      </c>
-      <c r="L32" s="9">
+      <c r="K32" s="13">
+        <v>1</v>
+      </c>
+      <c r="L32" s="8">
         <f t="shared" si="2"/>
         <v>5619</v>
       </c>
-      <c r="N32" s="14">
-        <v>1</v>
-      </c>
-      <c r="O32" s="9">
+      <c r="N32" s="13">
+        <v>1</v>
+      </c>
+      <c r="O32" s="8">
         <f t="shared" si="3"/>
         <v>5619</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="37"/>
-      <c r="B33" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C33" s="8" t="s">
+      <c r="A33" s="38"/>
+      <c r="B33" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="15">
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="14">
         <v>8</v>
       </c>
-      <c r="H33" s="14">
+      <c r="H33" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I33" s="9">
+      <c r="I33" s="8">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="K33" s="14">
-        <v>1</v>
-      </c>
-      <c r="L33" s="9">
+      <c r="K33" s="13">
+        <v>1</v>
+      </c>
+      <c r="L33" s="8">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="N33" s="14">
-        <v>1</v>
-      </c>
-      <c r="O33" s="9">
+      <c r="N33" s="13">
+        <v>1</v>
+      </c>
+      <c r="O33" s="8">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="37"/>
-      <c r="B34" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C34" s="8" t="s">
+      <c r="A34" s="38"/>
+      <c r="B34" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="15">
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="14">
         <v>1070</v>
       </c>
-      <c r="H34" s="14">
+      <c r="H34" s="13">
         <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
-      <c r="I34" s="9">
+      <c r="I34" s="8">
         <f t="shared" si="1"/>
         <v>267.5</v>
       </c>
-      <c r="K34" s="14">
+      <c r="K34" s="13">
         <v>0.25</v>
       </c>
-      <c r="L34" s="9">
+      <c r="L34" s="8">
         <f t="shared" si="2"/>
         <v>267.5</v>
       </c>
-      <c r="N34" s="14">
+      <c r="N34" s="13">
         <v>0.25</v>
       </c>
-      <c r="O34" s="9">
+      <c r="O34" s="8">
         <f t="shared" si="3"/>
         <v>267.5</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="16" t="s">
+      <c r="A36" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="B36" s="16" t="s">
+      <c r="B36" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
-      <c r="H36" s="16"/>
-      <c r="I36" s="23" t="s">
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="22" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="24" t="s">
+      <c r="A37" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="8"/>
-      <c r="I37" s="25" t="s">
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="24" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="24" t="s">
+      <c r="A38" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
-      <c r="H38" s="8"/>
-      <c r="I38" s="25" t="s">
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="24" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="24" t="s">
+      <c r="A39" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="8"/>
-      <c r="I39" s="25" t="s">
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
+      <c r="H39" s="7"/>
+      <c r="I39" s="24" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="40" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="7"/>
-      <c r="B40" s="8"/>
-      <c r="I40" s="1"/>
+      <c r="A40" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B40" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="I40" s="24" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="41" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="20"/>
-      <c r="B41" s="20"/>
-      <c r="C41" s="20"/>
-      <c r="D41" s="20"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="20"/>
-      <c r="G41" s="20"/>
-      <c r="H41" s="28" t="s">
+      <c r="A41" s="19"/>
+      <c r="B41" s="19"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="I41" s="29">
+      <c r="I41" s="28">
         <f>SUM(I10:I39)</f>
         <v>36152.9</v>
       </c>
     </row>
     <row r="42" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="43" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="24" t="s">
+      <c r="A43" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8">
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="7">
         <v>272</v>
       </c>
-      <c r="H43" s="9">
+      <c r="H43" s="8">
         <f>-N13</f>
         <v>-0.5</v>
       </c>
-      <c r="I43" s="22">
+      <c r="I43" s="21">
         <f t="shared" ref="I43" si="4">G43*H43</f>
         <v>-136</v>
       </c>
-      <c r="K43" s="13"/>
+      <c r="K43" s="12"/>
     </row>
     <row r="44" spans="1:15" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="27" t="s">
+      <c r="A44" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="B44" s="38" t="s">
+      <c r="B44" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="C44" s="38"/>
-      <c r="D44" s="38"/>
-      <c r="E44" s="38"/>
-      <c r="F44" s="38"/>
-      <c r="G44" s="8"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="30">
+      <c r="C44" s="39"/>
+      <c r="D44" s="39"/>
+      <c r="E44" s="39"/>
+      <c r="F44" s="39"/>
+      <c r="G44" s="7"/>
+      <c r="H44" s="13"/>
+      <c r="I44" s="29">
         <f>-O49</f>
         <v>-12360.5</v>
       </c>
-      <c r="K44" s="13"/>
+      <c r="K44" s="12"/>
     </row>
     <row r="45" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="7"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="14"/>
-      <c r="K45" s="13"/>
+      <c r="A45" s="6"/>
+      <c r="H45" s="13"/>
+      <c r="I45" s="13"/>
+      <c r="K45" s="12"/>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A46" s="7"/>
+      <c r="A46" s="6"/>
     </row>
     <row r="47" spans="1:15" ht="26" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="26"/>
-      <c r="B47" s="26"/>
-      <c r="C47" s="26"/>
-      <c r="D47" s="26"/>
-      <c r="E47" s="26"/>
-      <c r="F47" s="26"/>
-      <c r="G47" s="26"/>
-      <c r="H47" s="32" t="s">
+      <c r="A47" s="25"/>
+      <c r="B47" s="25"/>
+      <c r="C47" s="25"/>
+      <c r="D47" s="25"/>
+      <c r="E47" s="25"/>
+      <c r="F47" s="25"/>
+      <c r="G47" s="25"/>
+      <c r="H47" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="I47" s="40">
+      <c r="I47" s="33">
         <f>I41+SUM(I43:I45)</f>
         <v>23656.400000000001</v>
       </c>
-      <c r="L47" s="21">
+      <c r="L47" s="20">
         <f>SUM(L10:L46)</f>
         <v>36152.9</v>
       </c>
-      <c r="O47" s="21">
+      <c r="O47" s="20">
         <f>SUM(O10:O46)</f>
         <v>23792.400000000001</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A48" s="33" t="s">
+      <c r="A48" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="B48" s="33"/>
-      <c r="C48" s="33"/>
-      <c r="D48" s="33"/>
-      <c r="E48" s="33"/>
-      <c r="F48" s="33"/>
-      <c r="G48" s="33"/>
-      <c r="I48" s="10" t="str">
+      <c r="B48" s="34"/>
+      <c r="C48" s="34"/>
+      <c r="D48" s="34"/>
+      <c r="E48" s="34"/>
+      <c r="F48" s="34"/>
+      <c r="G48" s="34"/>
+      <c r="I48" s="9" t="str">
         <f>"+taxes"</f>
         <v>+taxes</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A49" s="33"/>
-      <c r="B49" s="33"/>
-      <c r="C49" s="33"/>
-      <c r="D49" s="33"/>
-      <c r="E49" s="33"/>
-      <c r="F49" s="33"/>
-      <c r="G49" s="33"/>
-      <c r="O49" s="12">
+      <c r="A49" s="34"/>
+      <c r="B49" s="34"/>
+      <c r="C49" s="34"/>
+      <c r="D49" s="34"/>
+      <c r="E49" s="34"/>
+      <c r="F49" s="34"/>
+      <c r="G49" s="34"/>
+      <c r="O49" s="11">
         <f>L47-O47</f>
         <v>12360.5</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A50" s="33"/>
-      <c r="B50" s="33"/>
-      <c r="C50" s="33"/>
-      <c r="D50" s="33"/>
-      <c r="E50" s="33"/>
-      <c r="F50" s="33"/>
-      <c r="G50" s="33"/>
+      <c r="A50" s="34"/>
+      <c r="B50" s="34"/>
+      <c r="C50" s="34"/>
+      <c r="D50" s="34"/>
+      <c r="E50" s="34"/>
+      <c r="F50" s="34"/>
+      <c r="G50" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/admin/Soumissions.xlsx
+++ b/admin/Soumissions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Business/GestionTechnologies/Migration4O/admin/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sylvain/Development/migration4o/admin/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2183DC64-95A7-3A42-8492-82BFDADE20AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{644A2981-E796-0646-8916-7591AC6AF846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8140" yWindow="1040" windowWidth="34440" windowHeight="30180" xr2:uid="{95DA9C45-7881-A84A-8BA8-7F5BDDABCE18}"/>
+    <workbookView xWindow="3880" yWindow="500" windowWidth="29720" windowHeight="19100" xr2:uid="{95DA9C45-7881-A84A-8BA8-7F5BDDABCE18}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="59">
   <si>
     <t>SOUMISSION</t>
   </si>
@@ -71,9 +71,6 @@
     <t>Configurations SSI</t>
   </si>
   <si>
-    <t>Documents</t>
-  </si>
-  <si>
     <t>Rapports central</t>
   </si>
   <si>
@@ -198,10 +195,6 @@
   </si>
   <si>
     <t>Export:</t>
-  </si>
-  <si>
-    <t>Collaboration spéciale de départ, taux 50% pour
-dossiers adresse, maintenances et préventions</t>
   </si>
   <si>
     <r>
@@ -267,16 +260,19 @@
     </r>
   </si>
   <si>
-    <t>#2026-03-12-A</t>
-  </si>
-  <si>
     <t>Date BD PL:</t>
   </si>
   <si>
-    <t>Ré-exports:</t>
-  </si>
-  <si>
-    <t>Deux exports complets additionnels, au maximum 18 mois après le premier export</t>
+    <t>#2026-04-17-A</t>
+  </si>
+  <si>
+    <t>Quatre (4) exports: 1=estimation/essai, 2=sûreté complète, 3=pré-migration, 4=migration finale</t>
+  </si>
+  <si>
+    <t>SPÉCIAL 2</t>
+  </si>
+  <si>
+    <t>Documents et pièces jointes pour toutes les activités</t>
   </si>
 </sst>
 </file>
@@ -365,7 +361,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -387,12 +383,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -498,15 +488,16 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -525,14 +516,18 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Currency" xfId="2" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="24">
+    <dxf>
+      <font>
+        <color rgb="FF0070C0"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color theme="5"/>
@@ -551,6 +546,21 @@
     <dxf>
       <font>
         <color rgb="FF0070C0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="5"/>
       </font>
     </dxf>
     <dxf>
@@ -595,7 +605,12 @@
     </dxf>
     <dxf>
       <font>
-        <color theme="5"/>
+        <color rgb="FF0070C0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
       </font>
     </dxf>
     <dxf>
@@ -605,12 +620,7 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0070C0"/>
+        <color theme="5"/>
       </font>
     </dxf>
     <dxf>
@@ -1018,7 +1028,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47DEBCEF-0F7F-5346-982E-C6834D7A1CED}">
-  <dimension ref="A1:O50"/>
+  <dimension ref="A1:S50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="2" customWidth="1"/>
@@ -1031,20 +1041,20 @@
     <col min="10" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="I1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="22" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" ht="22" x14ac:dyDescent="0.3">
       <c r="I2" s="10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I3" s="6"/>
     </row>
-    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
         <v>1</v>
       </c>
@@ -1052,35 +1062,39 @@
         <v>2</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="I4" s="32">
+        <v>54</v>
+      </c>
+      <c r="I4" s="31">
         <v>46077</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C5" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R5" s="33"/>
+    </row>
+    <row r="6" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C6" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="K7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>6</v>
       </c>
@@ -1093,30 +1107,36 @@
         <v>7</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>8</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L9" s="4" t="s">
         <v>8</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O9" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="35" t="s">
-        <v>41</v>
+      <c r="R9" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="S9" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="36" t="s">
+        <v>40</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>9</v>
@@ -1128,12 +1148,11 @@
         <v>1</v>
       </c>
       <c r="H10" s="13">
-        <f>K10</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I10" s="8">
         <f>G10*H10</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K10" s="13">
         <v>1</v>
@@ -1143,20 +1162,29 @@
         <v>1</v>
       </c>
       <c r="N10" s="13">
+        <f>N$37</f>
         <v>1</v>
       </c>
       <c r="O10" s="8">
         <f>$G10*N10</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="35"/>
+      <c r="R10" s="13">
+        <f>R$37</f>
+        <v>0.5</v>
+      </c>
+      <c r="S10" s="8">
+        <f>$G10*R10</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="36"/>
       <c r="B11" s="23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
@@ -1165,35 +1193,41 @@
         <v>66129</v>
       </c>
       <c r="H11" s="13">
-        <f t="shared" ref="H11:H34" si="0">K11</f>
         <v>0.05</v>
       </c>
       <c r="I11" s="8">
-        <f t="shared" ref="I11:I34" si="1">G11*H11</f>
+        <f t="shared" ref="I11:I34" si="0">G11*H11</f>
         <v>3306.4500000000003</v>
       </c>
       <c r="K11" s="13">
         <v>0.05</v>
       </c>
       <c r="L11" s="8">
-        <f t="shared" ref="L11:L34" si="2">$G11*K11</f>
+        <f t="shared" ref="L11:L34" si="1">$G11*K11</f>
         <v>3306.4500000000003</v>
       </c>
       <c r="N11" s="13">
         <v>0.05</v>
       </c>
       <c r="O11" s="8">
-        <f t="shared" ref="O11:O34" si="3">$G11*N11</f>
+        <f t="shared" ref="O11:O34" si="2">$G11*N11</f>
         <v>3306.4500000000003</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="36"/>
+      <c r="R11" s="13">
+        <v>0.05</v>
+      </c>
+      <c r="S11" s="8">
+        <f t="shared" ref="S11:S34" si="3">$G11*R11</f>
+        <v>3306.4500000000003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="37"/>
       <c r="B12" s="23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
@@ -1202,37 +1236,45 @@
         <v>2</v>
       </c>
       <c r="H12" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="I12" s="8">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I12" s="8">
+      <c r="K12" s="13">
+        <v>1</v>
+      </c>
+      <c r="L12" s="8">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="K12" s="13">
-        <v>1</v>
-      </c>
-      <c r="L12" s="8">
+      <c r="N12" s="13">
+        <f>N$37</f>
+        <v>1</v>
+      </c>
+      <c r="O12" s="8">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N12" s="13">
-        <v>1</v>
-      </c>
-      <c r="O12" s="8">
+      <c r="R12" s="13">
+        <f>R$37</f>
+        <v>0.5</v>
+      </c>
+      <c r="S12" s="8">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="37" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="30" t="s">
-        <v>33</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>32</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D13" s="15"/>
       <c r="E13" s="15"/>
@@ -1241,35 +1283,43 @@
         <v>6266</v>
       </c>
       <c r="H13" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="I13" s="18">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I13" s="18">
+        <v>1879.8</v>
+      </c>
+      <c r="K13" s="17">
+        <v>1</v>
+      </c>
+      <c r="L13" s="8">
         <f t="shared" si="1"/>
         <v>6266</v>
       </c>
-      <c r="K13" s="17">
-        <v>1</v>
-      </c>
-      <c r="L13" s="8">
+      <c r="N13" s="17">
+        <f>N$38</f>
+        <v>0.5</v>
+      </c>
+      <c r="O13" s="8">
         <f t="shared" si="2"/>
-        <v>6266</v>
-      </c>
-      <c r="N13" s="17">
-        <v>0.5</v>
-      </c>
-      <c r="O13" s="8">
+        <v>3133</v>
+      </c>
+      <c r="R13" s="17">
+        <f>R$38</f>
+        <v>0.3</v>
+      </c>
+      <c r="S13" s="8">
         <f t="shared" si="3"/>
-        <v>3133</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="35"/>
+        <v>1879.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="36"/>
       <c r="B14" s="23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
@@ -1278,35 +1328,41 @@
         <v>14179</v>
       </c>
       <c r="H14" s="13">
+        <v>0.05</v>
+      </c>
+      <c r="I14" s="8">
         <f t="shared" si="0"/>
+        <v>708.95</v>
+      </c>
+      <c r="K14" s="13">
         <v>0.05</v>
       </c>
-      <c r="I14" s="8">
+      <c r="L14" s="8">
         <f t="shared" si="1"/>
         <v>708.95</v>
       </c>
-      <c r="K14" s="13">
+      <c r="N14" s="13">
         <v>0.05</v>
       </c>
-      <c r="L14" s="8">
+      <c r="O14" s="8">
         <f t="shared" si="2"/>
         <v>708.95</v>
       </c>
-      <c r="N14" s="13">
+      <c r="R14" s="13">
         <v>0.05</v>
       </c>
-      <c r="O14" s="8">
+      <c r="S14" s="8">
         <f t="shared" si="3"/>
         <v>708.95</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="35"/>
+    <row r="15" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="36"/>
       <c r="B15" s="23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
@@ -1315,35 +1371,43 @@
         <v>46</v>
       </c>
       <c r="H15" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="I15" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I15" s="8">
+        <v>23</v>
+      </c>
+      <c r="K15" s="13">
+        <v>1</v>
+      </c>
+      <c r="L15" s="8">
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
-      <c r="K15" s="13">
-        <v>1</v>
-      </c>
-      <c r="L15" s="8">
+      <c r="N15" s="13">
+        <f t="shared" ref="N15:N20" si="4">N$37</f>
+        <v>1</v>
+      </c>
+      <c r="O15" s="8">
         <f t="shared" si="2"/>
         <v>46</v>
       </c>
-      <c r="N15" s="13">
-        <v>1</v>
-      </c>
-      <c r="O15" s="8">
+      <c r="R15" s="13">
+        <f t="shared" ref="R15:R20" si="5">R$37</f>
+        <v>0.5</v>
+      </c>
+      <c r="S15" s="8">
         <f t="shared" si="3"/>
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="35"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="36"/>
       <c r="B16" s="23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
@@ -1352,35 +1416,43 @@
         <v>1</v>
       </c>
       <c r="H16" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="I16" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I16" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="K16" s="13">
+        <v>1</v>
+      </c>
+      <c r="L16" s="8">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K16" s="13">
-        <v>1</v>
-      </c>
-      <c r="L16" s="8">
+      <c r="N16" s="13">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="O16" s="8">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="N16" s="13">
-        <v>1</v>
-      </c>
-      <c r="O16" s="8">
+      <c r="R16" s="13">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="S16" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="36"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="37"/>
       <c r="B17" s="23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
@@ -1389,37 +1461,45 @@
         <v>0</v>
       </c>
       <c r="H17" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="I17" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I17" s="8">
+        <v>0</v>
+      </c>
+      <c r="K17" s="13">
+        <v>1</v>
+      </c>
+      <c r="L17" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K17" s="13">
-        <v>1</v>
-      </c>
-      <c r="L17" s="8">
+      <c r="N17" s="13">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="O17" s="8">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N17" s="13">
-        <v>1</v>
-      </c>
-      <c r="O17" s="8">
+      <c r="R17" s="13">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="S17" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="37" t="s">
-        <v>43</v>
-      </c>
-      <c r="B18" s="30" t="s">
-        <v>33</v>
+    <row r="18" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="29" t="s">
+        <v>32</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D18" s="15"/>
       <c r="E18" s="15"/>
@@ -1428,35 +1508,43 @@
         <v>4</v>
       </c>
       <c r="H18" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="I18" s="18">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I18" s="18">
+        <v>2</v>
+      </c>
+      <c r="K18" s="17">
+        <v>1</v>
+      </c>
+      <c r="L18" s="8">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="K18" s="17">
-        <v>1</v>
-      </c>
-      <c r="L18" s="8">
+      <c r="N18" s="17">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="O18" s="8">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="N18" s="17">
-        <v>1</v>
-      </c>
-      <c r="O18" s="8">
+      <c r="R18" s="17">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="S18" s="8">
         <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="35"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="36"/>
       <c r="B19" s="23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
@@ -1465,35 +1553,43 @@
         <v>28</v>
       </c>
       <c r="H19" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="I19" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I19" s="8">
+        <v>14</v>
+      </c>
+      <c r="K19" s="13">
+        <v>1</v>
+      </c>
+      <c r="L19" s="8">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
-      <c r="K19" s="13">
-        <v>1</v>
-      </c>
-      <c r="L19" s="8">
+      <c r="N19" s="13">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="O19" s="8">
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="N19" s="13">
-        <v>1</v>
-      </c>
-      <c r="O19" s="8">
+      <c r="R19" s="13">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="S19" s="8">
         <f t="shared" si="3"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="35"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="36"/>
       <c r="B20" s="23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
@@ -1502,35 +1598,43 @@
         <v>523</v>
       </c>
       <c r="H20" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="I20" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I20" s="8">
+        <v>261.5</v>
+      </c>
+      <c r="K20" s="13">
+        <v>1</v>
+      </c>
+      <c r="L20" s="8">
         <f t="shared" si="1"/>
         <v>523</v>
       </c>
-      <c r="K20" s="13">
-        <v>1</v>
-      </c>
-      <c r="L20" s="8">
+      <c r="N20" s="13">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="O20" s="8">
         <f t="shared" si="2"/>
         <v>523</v>
       </c>
-      <c r="N20" s="13">
-        <v>1</v>
-      </c>
-      <c r="O20" s="8">
+      <c r="R20" s="13">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="S20" s="8">
         <f t="shared" si="3"/>
-        <v>523</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="35"/>
+        <v>261.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="36"/>
       <c r="B21" s="23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
@@ -1539,35 +1643,43 @@
         <v>2556</v>
       </c>
       <c r="H21" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="I21" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I21" s="8">
+        <v>766.8</v>
+      </c>
+      <c r="K21" s="13">
+        <v>1</v>
+      </c>
+      <c r="L21" s="8">
         <f t="shared" si="1"/>
         <v>2556</v>
       </c>
-      <c r="K21" s="13">
-        <v>1</v>
-      </c>
-      <c r="L21" s="8">
+      <c r="N21" s="13">
+        <f>N$38</f>
+        <v>0.5</v>
+      </c>
+      <c r="O21" s="8">
         <f t="shared" si="2"/>
-        <v>2556</v>
-      </c>
-      <c r="N21" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="O21" s="8">
+        <v>1278</v>
+      </c>
+      <c r="R21" s="13">
+        <f>R$38</f>
+        <v>0.3</v>
+      </c>
+      <c r="S21" s="8">
         <f t="shared" si="3"/>
-        <v>1278</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="35"/>
+        <v>766.8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="36"/>
       <c r="B22" s="23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
@@ -1576,35 +1688,43 @@
         <v>523</v>
       </c>
       <c r="H22" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="I22" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I22" s="8">
+        <v>261.5</v>
+      </c>
+      <c r="K22" s="13">
+        <v>1</v>
+      </c>
+      <c r="L22" s="8">
         <f t="shared" si="1"/>
         <v>523</v>
       </c>
-      <c r="K22" s="13">
-        <v>1</v>
-      </c>
-      <c r="L22" s="8">
+      <c r="N22" s="13">
+        <f>N$37</f>
+        <v>1</v>
+      </c>
+      <c r="O22" s="8">
         <f t="shared" si="2"/>
         <v>523</v>
       </c>
-      <c r="N22" s="13">
-        <v>1</v>
-      </c>
-      <c r="O22" s="8">
+      <c r="R22" s="13">
+        <f>R$37</f>
+        <v>0.5</v>
+      </c>
+      <c r="S22" s="8">
         <f t="shared" si="3"/>
-        <v>523</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="36"/>
+        <v>261.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="37"/>
       <c r="B23" s="23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
@@ -1613,37 +1733,45 @@
         <v>1309</v>
       </c>
       <c r="H23" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="I23" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I23" s="8">
+        <v>392.7</v>
+      </c>
+      <c r="K23" s="13">
+        <v>1</v>
+      </c>
+      <c r="L23" s="8">
         <f t="shared" si="1"/>
         <v>1309</v>
       </c>
-      <c r="K23" s="13">
-        <v>1</v>
-      </c>
-      <c r="L23" s="8">
+      <c r="N23" s="13">
+        <f>N$38</f>
+        <v>0.5</v>
+      </c>
+      <c r="O23" s="8">
         <f t="shared" si="2"/>
-        <v>1309</v>
-      </c>
-      <c r="N23" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="O23" s="8">
+        <v>654.5</v>
+      </c>
+      <c r="R23" s="13">
+        <f>R$38</f>
+        <v>0.3</v>
+      </c>
+      <c r="S23" s="8">
         <f t="shared" si="3"/>
-        <v>654.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="37" t="s">
-        <v>44</v>
-      </c>
-      <c r="B24" s="30" t="s">
-        <v>33</v>
+        <v>392.7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="29" t="s">
+        <v>32</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D24" s="15"/>
       <c r="E24" s="15"/>
@@ -1652,35 +1780,43 @@
         <v>121</v>
       </c>
       <c r="H24" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="I24" s="18">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I24" s="18">
+        <v>60.5</v>
+      </c>
+      <c r="K24" s="17">
+        <v>1</v>
+      </c>
+      <c r="L24" s="8">
         <f t="shared" si="1"/>
         <v>121</v>
       </c>
-      <c r="K24" s="17">
-        <v>1</v>
-      </c>
-      <c r="L24" s="8">
+      <c r="N24" s="17">
+        <f>N$37</f>
+        <v>1</v>
+      </c>
+      <c r="O24" s="8">
         <f t="shared" si="2"/>
         <v>121</v>
       </c>
-      <c r="N24" s="17">
-        <v>1</v>
-      </c>
-      <c r="O24" s="8">
+      <c r="R24" s="17">
+        <f>R$37</f>
+        <v>0.5</v>
+      </c>
+      <c r="S24" s="8">
         <f t="shared" si="3"/>
-        <v>121</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="35"/>
+        <v>60.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="36"/>
       <c r="B25" s="23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
@@ -1689,35 +1825,43 @@
         <v>7</v>
       </c>
       <c r="H25" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="I25" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I25" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="K25" s="13">
+        <v>1</v>
+      </c>
+      <c r="L25" s="8">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="K25" s="13">
-        <v>1</v>
-      </c>
-      <c r="L25" s="8">
+      <c r="N25" s="13">
+        <f>N$37</f>
+        <v>1</v>
+      </c>
+      <c r="O25" s="8">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="N25" s="13">
-        <v>1</v>
-      </c>
-      <c r="O25" s="8">
+      <c r="R25" s="13">
+        <f>R$37</f>
+        <v>0.5</v>
+      </c>
+      <c r="S25" s="8">
         <f t="shared" si="3"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="35"/>
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="36"/>
       <c r="B26" s="23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
@@ -1726,35 +1870,43 @@
         <v>3</v>
       </c>
       <c r="H26" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="I26" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I26" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="K26" s="13">
+        <v>1</v>
+      </c>
+      <c r="L26" s="8">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K26" s="13">
-        <v>1</v>
-      </c>
-      <c r="L26" s="8">
+      <c r="N26" s="13">
+        <f>N$37</f>
+        <v>1</v>
+      </c>
+      <c r="O26" s="8">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="N26" s="13">
-        <v>1</v>
-      </c>
-      <c r="O26" s="8">
+      <c r="R26" s="13">
+        <f>R$37</f>
+        <v>0.5</v>
+      </c>
+      <c r="S26" s="8">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="35"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="36"/>
       <c r="B27" s="23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
@@ -1763,35 +1915,43 @@
         <v>1</v>
       </c>
       <c r="H27" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="I27" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I27" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="K27" s="13">
+        <v>1</v>
+      </c>
+      <c r="L27" s="8">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K27" s="13">
-        <v>1</v>
-      </c>
-      <c r="L27" s="8">
+      <c r="N27" s="13">
+        <f>N$37</f>
+        <v>1</v>
+      </c>
+      <c r="O27" s="8">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="N27" s="13">
-        <v>1</v>
-      </c>
-      <c r="O27" s="8">
+      <c r="R27" s="13">
+        <f>R$37</f>
+        <v>0.5</v>
+      </c>
+      <c r="S27" s="8">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="35"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="36"/>
       <c r="B28" s="23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
@@ -1800,35 +1960,43 @@
         <v>0</v>
       </c>
       <c r="H28" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="I28" s="8">
         <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="13">
         <v>0.25</v>
       </c>
-      <c r="I28" s="8">
+      <c r="L28" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K28" s="13">
+      <c r="N28" s="13">
+        <f>N$39</f>
         <v>0.25</v>
       </c>
-      <c r="L28" s="8">
+      <c r="O28" s="8">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N28" s="13">
-        <v>0.25</v>
-      </c>
-      <c r="O28" s="8">
+      <c r="R28" s="13">
+        <f>R$39</f>
+        <v>0.1</v>
+      </c>
+      <c r="S28" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="36"/>
+    <row r="29" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="37"/>
       <c r="B29" s="23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
@@ -1837,37 +2005,45 @@
         <v>0</v>
       </c>
       <c r="H29" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="I29" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I29" s="8">
+        <v>0</v>
+      </c>
+      <c r="K29" s="13">
+        <v>1</v>
+      </c>
+      <c r="L29" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K29" s="13">
-        <v>1</v>
-      </c>
-      <c r="L29" s="8">
+      <c r="N29" s="13">
+        <f>N$37</f>
+        <v>1</v>
+      </c>
+      <c r="O29" s="8">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N29" s="13">
-        <v>1</v>
-      </c>
-      <c r="O29" s="8">
+      <c r="R29" s="13">
+        <f>R$37</f>
+        <v>0.5</v>
+      </c>
+      <c r="S29" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="B30" s="30" t="s">
-        <v>33</v>
+    <row r="30" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="29" t="s">
+        <v>32</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D30" s="15"/>
       <c r="E30" s="15"/>
@@ -1876,35 +2052,43 @@
         <v>14590</v>
       </c>
       <c r="H30" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="I30" s="18">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I30" s="18">
+        <v>4377</v>
+      </c>
+      <c r="K30" s="17">
+        <v>1</v>
+      </c>
+      <c r="L30" s="8">
         <f t="shared" si="1"/>
         <v>14590</v>
       </c>
-      <c r="K30" s="17">
-        <v>1</v>
-      </c>
-      <c r="L30" s="8">
+      <c r="N30" s="17">
+        <f>N$38</f>
+        <v>0.5</v>
+      </c>
+      <c r="O30" s="8">
         <f t="shared" si="2"/>
-        <v>14590</v>
-      </c>
-      <c r="N30" s="17">
-        <v>0.5</v>
-      </c>
-      <c r="O30" s="8">
+        <v>7295</v>
+      </c>
+      <c r="R30" s="17">
+        <f>R$38</f>
+        <v>0.3</v>
+      </c>
+      <c r="S30" s="8">
         <f t="shared" si="3"/>
-        <v>7295</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="38"/>
+        <v>4377</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="39"/>
       <c r="B31" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" s="7" t="s">
         <v>33</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>34</v>
       </c>
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
@@ -1913,35 +2097,43 @@
         <v>1048</v>
       </c>
       <c r="H31" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="I31" s="8">
         <f t="shared" si="0"/>
+        <v>104.80000000000001</v>
+      </c>
+      <c r="K31" s="13">
         <v>0.25</v>
       </c>
-      <c r="I31" s="8">
+      <c r="L31" s="8">
         <f t="shared" si="1"/>
         <v>262</v>
       </c>
-      <c r="K31" s="13">
+      <c r="N31" s="13">
+        <f>N$39</f>
         <v>0.25</v>
       </c>
-      <c r="L31" s="8">
+      <c r="O31" s="8">
         <f t="shared" si="2"/>
         <v>262</v>
       </c>
-      <c r="N31" s="13">
-        <v>0.25</v>
-      </c>
-      <c r="O31" s="8">
+      <c r="R31" s="13">
+        <f>R$39</f>
+        <v>0.1</v>
+      </c>
+      <c r="S31" s="8">
         <f t="shared" si="3"/>
-        <v>262</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="38"/>
+        <v>104.80000000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="39"/>
       <c r="B32" s="23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
@@ -1950,35 +2142,43 @@
         <v>5619</v>
       </c>
       <c r="H32" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="I32" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I32" s="8">
+        <v>2809.5</v>
+      </c>
+      <c r="K32" s="13">
+        <v>1</v>
+      </c>
+      <c r="L32" s="8">
         <f t="shared" si="1"/>
         <v>5619</v>
       </c>
-      <c r="K32" s="13">
-        <v>1</v>
-      </c>
-      <c r="L32" s="8">
+      <c r="N32" s="13">
+        <f>N$37</f>
+        <v>1</v>
+      </c>
+      <c r="O32" s="8">
         <f t="shared" si="2"/>
         <v>5619</v>
       </c>
-      <c r="N32" s="13">
-        <v>1</v>
-      </c>
-      <c r="O32" s="8">
+      <c r="R32" s="13">
+        <f>R$37</f>
+        <v>0.5</v>
+      </c>
+      <c r="S32" s="8">
         <f t="shared" si="3"/>
-        <v>5619</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="38"/>
+        <v>2809.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="39"/>
       <c r="B33" s="23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
@@ -1987,35 +2187,43 @@
         <v>8</v>
       </c>
       <c r="H33" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="I33" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I33" s="8">
+        <v>4</v>
+      </c>
+      <c r="K33" s="13">
+        <v>1</v>
+      </c>
+      <c r="L33" s="8">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="K33" s="13">
-        <v>1</v>
-      </c>
-      <c r="L33" s="8">
+      <c r="N33" s="13">
+        <f>N$37</f>
+        <v>1</v>
+      </c>
+      <c r="O33" s="8">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="N33" s="13">
-        <v>1</v>
-      </c>
-      <c r="O33" s="8">
+      <c r="R33" s="13">
+        <f>R$37</f>
+        <v>0.5</v>
+      </c>
+      <c r="S33" s="8">
         <f t="shared" si="3"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="38"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="39"/>
       <c r="B34" s="23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
@@ -2024,35 +2232,43 @@
         <v>1070</v>
       </c>
       <c r="H34" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="I34" s="8">
         <f t="shared" si="0"/>
+        <v>107</v>
+      </c>
+      <c r="K34" s="13">
         <v>0.25</v>
       </c>
-      <c r="I34" s="8">
+      <c r="L34" s="8">
         <f t="shared" si="1"/>
         <v>267.5</v>
       </c>
-      <c r="K34" s="13">
+      <c r="N34" s="13">
+        <f>N$39</f>
         <v>0.25</v>
       </c>
-      <c r="L34" s="8">
+      <c r="O34" s="8">
         <f t="shared" si="2"/>
         <v>267.5</v>
       </c>
-      <c r="N34" s="13">
-        <v>0.25</v>
-      </c>
-      <c r="O34" s="8">
+      <c r="R34" s="13">
+        <f>R$39</f>
+        <v>0.1</v>
+      </c>
+      <c r="S34" s="8">
         <f t="shared" si="3"/>
-        <v>267.5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="15" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C36" s="15"/>
       <c r="D36" s="15"/>
@@ -2061,15 +2277,13 @@
       <c r="G36" s="15"/>
       <c r="H36" s="15"/>
       <c r="I36" s="22" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="23" t="s">
-        <v>52</v>
-      </c>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="23"/>
       <c r="B37" s="7" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
@@ -2078,15 +2292,21 @@
       <c r="G37" s="7"/>
       <c r="H37" s="7"/>
       <c r="I37" s="24" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+      <c r="N37" s="33">
+        <v>1</v>
+      </c>
+      <c r="R37" s="33">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
@@ -2095,15 +2315,19 @@
       <c r="G38" s="7"/>
       <c r="H38" s="7"/>
       <c r="I38" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="N38" s="33">
+        <v>0.5</v>
+      </c>
+      <c r="R38" s="33">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="23"/>
+      <c r="B39" s="7" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>39</v>
       </c>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
@@ -2112,21 +2336,31 @@
       <c r="G39" s="7"/>
       <c r="H39" s="7"/>
       <c r="I39" s="24" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B40" s="40" t="s">
-        <v>59</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="N39" s="33">
+        <v>0.25</v>
+      </c>
+      <c r="R39" s="33">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="23"/>
+      <c r="B40" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
+      <c r="H40" s="7"/>
       <c r="I40" s="24" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="19"/>
       <c r="B41" s="19"/>
       <c r="C41" s="19"/>
@@ -2135,20 +2369,20 @@
       <c r="F41" s="19"/>
       <c r="G41" s="19"/>
       <c r="H41" s="27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I41" s="28">
         <f>SUM(I10:I39)</f>
-        <v>36152.9</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>15087</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
@@ -2162,40 +2396,33 @@
         <v>-0.5</v>
       </c>
       <c r="I43" s="21">
-        <f t="shared" ref="I43" si="4">G43*H43</f>
+        <f t="shared" ref="I43" si="6">G43*H43</f>
         <v>-136</v>
       </c>
       <c r="K43" s="12"/>
     </row>
-    <row r="44" spans="1:15" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B44" s="39" t="s">
-        <v>53</v>
-      </c>
-      <c r="C44" s="39"/>
-      <c r="D44" s="39"/>
-      <c r="E44" s="39"/>
-      <c r="F44" s="39"/>
+    <row r="44" spans="1:19" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="26"/>
+      <c r="B44" s="40"/>
+      <c r="C44" s="40"/>
+      <c r="D44" s="40"/>
+      <c r="E44" s="40"/>
+      <c r="F44" s="40"/>
       <c r="G44" s="7"/>
       <c r="H44" s="13"/>
-      <c r="I44" s="29">
-        <f>-O49</f>
-        <v>-12360.5</v>
-      </c>
+      <c r="I44" s="34"/>
       <c r="K44" s="12"/>
     </row>
-    <row r="45" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6"/>
       <c r="H45" s="13"/>
       <c r="I45" s="13"/>
       <c r="K45" s="12"/>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A46" s="6"/>
     </row>
-    <row r="47" spans="1:15" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" ht="26" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="25"/>
       <c r="B47" s="25"/>
       <c r="C47" s="25"/>
@@ -2203,12 +2430,12 @@
       <c r="E47" s="25"/>
       <c r="F47" s="25"/>
       <c r="G47" s="25"/>
-      <c r="H47" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="I47" s="33">
+      <c r="H47" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="I47" s="32">
         <f>I41+SUM(I43:I45)</f>
-        <v>23656.400000000001</v>
+        <v>14951</v>
       </c>
       <c r="L47" s="20">
         <f>SUM(L10:L46)</f>
@@ -2218,43 +2445,51 @@
         <f>SUM(O10:O46)</f>
         <v>23792.400000000001</v>
       </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A48" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="B48" s="34"/>
-      <c r="C48" s="34"/>
-      <c r="D48" s="34"/>
-      <c r="E48" s="34"/>
-      <c r="F48" s="34"/>
-      <c r="G48" s="34"/>
+      <c r="S47" s="20">
+        <f>SUM(S10:S46)</f>
+        <v>15087</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A48" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="B48" s="35"/>
+      <c r="C48" s="35"/>
+      <c r="D48" s="35"/>
+      <c r="E48" s="35"/>
+      <c r="F48" s="35"/>
+      <c r="G48" s="35"/>
       <c r="I48" s="9" t="str">
         <f>"+taxes"</f>
         <v>+taxes</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A49" s="34"/>
-      <c r="B49" s="34"/>
-      <c r="C49" s="34"/>
-      <c r="D49" s="34"/>
-      <c r="E49" s="34"/>
-      <c r="F49" s="34"/>
-      <c r="G49" s="34"/>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A49" s="35"/>
+      <c r="B49" s="35"/>
+      <c r="C49" s="35"/>
+      <c r="D49" s="35"/>
+      <c r="E49" s="35"/>
+      <c r="F49" s="35"/>
+      <c r="G49" s="35"/>
       <c r="O49" s="11">
         <f>L47-O47</f>
         <v>12360.5</v>
       </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A50" s="34"/>
-      <c r="B50" s="34"/>
-      <c r="C50" s="34"/>
-      <c r="D50" s="34"/>
-      <c r="E50" s="34"/>
-      <c r="F50" s="34"/>
-      <c r="G50" s="34"/>
+      <c r="S49" s="11">
+        <f>O47-S47</f>
+        <v>8705.4000000000015</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A50" s="35"/>
+      <c r="B50" s="35"/>
+      <c r="C50" s="35"/>
+      <c r="D50" s="35"/>
+      <c r="E50" s="35"/>
+      <c r="F50" s="35"/>
+      <c r="G50" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -2267,20 +2502,34 @@
     <mergeCell ref="B44:F44"/>
   </mergeCells>
   <conditionalFormatting sqref="H10:H34">
-    <cfRule type="cellIs" dxfId="19" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="5" operator="equal">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="6" operator="equal">
       <formula>0.25</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="7" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="8" operator="equal">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H43:H45">
+    <cfRule type="cellIs" dxfId="19" priority="28" operator="equal">
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="27" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="17" priority="26" operator="equal">
+      <formula>0.25</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="25" operator="equal">
+      <formula>0.05</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I45">
     <cfRule type="cellIs" dxfId="15" priority="13" operator="equal">
       <formula>0.05</formula>
     </cfRule>
@@ -2294,46 +2543,46 @@
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I45">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+  <conditionalFormatting sqref="K10:K34">
+    <cfRule type="cellIs" dxfId="11" priority="21" operator="equal">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="22" operator="equal">
       <formula>0.25</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="23" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
-      <formula>0.5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K10:K34">
-    <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
-      <formula>0.05</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="10" operator="equal">
-      <formula>0.25</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="11" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="24" operator="equal">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N10:N34">
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="4" operator="equal">
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
+      <formula>0.25</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="6" operator="equal">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R10:R34">
+    <cfRule type="cellIs" dxfId="3" priority="10" operator="equal">
       <formula>0.25</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="11" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="12" operator="equal">
       <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="9" operator="equal">
+      <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.31944444444444442" bottom="0.3888888888888889" header="0.3" footer="0.3"/>
